--- a/r5-ELGA-MOPED-256-Beispiele-für-maskierte-Ressourcen-erstellen/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-256-Beispiele-für-maskierte-Ressourcen-erstellen/StructureDefinition-MOPEDClaim.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6584" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6584" uniqueCount="798">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T14:27:25+00:00</t>
+    <t>2024-11-11T10:32:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1156,6 +1156,10 @@
   </si>
   <si>
     <t>Used in some jurisdictions to link clinical events to claim items.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profile:resolve()}
+</t>
   </si>
   <si>
     <t>Claim.encounter:MopedEncounter</t>
@@ -8146,7 +8150,7 @@
         <v>19</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>19</v>
+        <v>366</v>
       </c>
       <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
@@ -8182,13 +8186,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>359</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>19</v>
@@ -8210,10 +8214,10 @@
         <v>19</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M49" t="s" s="2">
         <v>363</v>
@@ -8297,13 +8301,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>359</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>19</v>
@@ -8325,10 +8329,10 @@
         <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M50" t="s" s="2">
         <v>363</v>
@@ -8412,10 +8416,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8438,17 +8442,17 @@
         <v>19</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>19</v>
@@ -8497,7 +8501,7 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -8515,7 +8519,7 @@
         <v>19</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>19</v>
@@ -8523,10 +8527,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8552,16 +8556,16 @@
         <v>205</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>19</v>
@@ -8590,7 +8594,7 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>19</v>
@@ -8608,7 +8612,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -8634,10 +8638,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8663,10 +8667,10 @@
         <v>284</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8717,7 +8721,7 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -8743,10 +8747,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8852,10 +8856,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8963,10 +8967,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9076,10 +9080,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9105,10 +9109,10 @@
         <v>205</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9139,7 +9143,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>19</v>
@@ -9157,7 +9161,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>87</v>
@@ -9183,10 +9187,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9209,13 +9213,13 @@
         <v>19</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9266,7 +9270,7 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>87</v>
@@ -9292,10 +9296,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9321,14 +9325,14 @@
         <v>284</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>19</v>
@@ -9377,7 +9381,7 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -9403,10 +9407,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9512,10 +9516,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9623,10 +9627,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9736,10 +9740,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9762,17 +9766,17 @@
         <v>19</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>19</v>
@@ -9821,7 +9825,7 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>87</v>
@@ -9847,10 +9851,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9873,17 +9877,17 @@
         <v>19</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>19</v>
@@ -9932,7 +9936,7 @@
         <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>87</v>
@@ -9950,7 +9954,7 @@
         <v>19</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>19</v>
@@ -9958,10 +9962,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9984,19 +9988,19 @@
         <v>19</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>19</v>
@@ -10045,7 +10049,7 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -10071,10 +10075,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10100,16 +10104,16 @@
         <v>205</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>19</v>
@@ -10137,10 +10141,10 @@
         <v>219</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>19</v>
@@ -10158,7 +10162,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -10184,10 +10188,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10213,14 +10217,14 @@
         <v>205</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>19</v>
@@ -10249,7 +10253,7 @@
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>19</v>
@@ -10267,7 +10271,7 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -10293,14 +10297,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10322,16 +10326,16 @@
         <v>284</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>19</v>
@@ -10380,7 +10384,7 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -10395,7 +10399,7 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>19</v>
@@ -10406,10 +10410,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10515,10 +10519,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10626,10 +10630,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10739,10 +10743,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10765,17 +10769,17 @@
         <v>19</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>19</v>
@@ -10824,7 +10828,7 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>87</v>
@@ -10850,10 +10854,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10879,16 +10883,16 @@
         <v>205</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>19</v>
@@ -10916,10 +10920,10 @@
         <v>219</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>19</v>
@@ -10937,7 +10941,7 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>87</v>
@@ -10963,10 +10967,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10992,14 +10996,14 @@
         <v>205</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>19</v>
@@ -11027,10 +11031,10 @@
         <v>219</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>19</v>
@@ -11048,7 +11052,7 @@
         <v>19</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -11074,10 +11078,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11100,13 +11104,13 @@
         <v>19</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11157,7 +11161,7 @@
         <v>19</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -11183,10 +11187,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11209,19 +11213,19 @@
         <v>19</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>19</v>
@@ -11270,7 +11274,7 @@
         <v>19</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -11296,10 +11300,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11325,16 +11329,16 @@
         <v>205</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>19</v>
@@ -11362,10 +11366,10 @@
         <v>219</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>19</v>
@@ -11383,7 +11387,7 @@
         <v>19</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -11409,10 +11413,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11438,14 +11442,14 @@
         <v>284</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>19</v>
@@ -11494,7 +11498,7 @@
         <v>19</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -11509,7 +11513,7 @@
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>19</v>
@@ -11520,10 +11524,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11629,10 +11633,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11740,10 +11744,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11853,10 +11857,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11879,19 +11883,19 @@
         <v>19</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>19</v>
@@ -11940,7 +11944,7 @@
         <v>19</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>87</v>
@@ -11966,10 +11970,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11992,17 +11996,17 @@
         <v>19</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>19</v>
@@ -12030,10 +12034,10 @@
         <v>219</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>19</v>
@@ -12051,7 +12055,7 @@
         <v>19</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>87</v>
@@ -12077,10 +12081,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12106,16 +12110,16 @@
         <v>205</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>19</v>
@@ -12143,10 +12147,10 @@
         <v>219</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>19</v>
@@ -12164,7 +12168,7 @@
         <v>19</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -12190,10 +12194,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12219,14 +12223,14 @@
         <v>205</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>19</v>
@@ -12254,10 +12258,10 @@
         <v>219</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>19</v>
@@ -12275,7 +12279,7 @@
         <v>19</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -12301,10 +12305,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12330,14 +12334,14 @@
         <v>284</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>19</v>
@@ -12386,7 +12390,7 @@
         <v>19</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -12412,10 +12416,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12521,10 +12525,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12628,13 +12632,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B89" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="B89" t="s" s="2">
-        <v>518</v>
-      </c>
       <c r="C89" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>19</v>
@@ -12656,13 +12660,13 @@
         <v>19</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12739,10 +12743,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12852,10 +12856,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12878,17 +12882,17 @@
         <v>19</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>19</v>
@@ -12937,7 +12941,7 @@
         <v>19</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>87</v>
@@ -12963,10 +12967,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12992,16 +12996,16 @@
         <v>205</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>19</v>
@@ -13029,10 +13033,10 @@
         <v>219</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>19</v>
@@ -13050,7 +13054,7 @@
         <v>19</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -13076,10 +13080,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13105,14 +13109,14 @@
         <v>243</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>19</v>
@@ -13161,7 +13165,7 @@
         <v>19</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -13187,10 +13191,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13213,17 +13217,17 @@
         <v>19</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>19</v>
@@ -13251,10 +13255,10 @@
         <v>219</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>19</v>
@@ -13272,7 +13276,7 @@
         <v>19</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>87</v>
@@ -13298,10 +13302,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13324,17 +13328,17 @@
         <v>19</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>19</v>
@@ -13383,7 +13387,7 @@
         <v>19</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -13409,10 +13413,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13438,16 +13442,16 @@
         <v>284</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>19</v>
@@ -13496,7 +13500,7 @@
         <v>19</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -13517,15 +13521,15 @@
         <v>19</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13631,10 +13635,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13742,10 +13746,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13855,10 +13859,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13881,17 +13885,17 @@
         <v>88</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>19</v>
@@ -13940,7 +13944,7 @@
         <v>19</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>87</v>
@@ -13966,10 +13970,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13992,19 +13996,19 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>19</v>
@@ -14053,7 +14057,7 @@
         <v>19</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>87</v>
@@ -14079,10 +14083,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14108,16 +14112,16 @@
         <v>185</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>19</v>
@@ -14166,7 +14170,7 @@
         <v>19</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -14192,10 +14196,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14218,17 +14222,17 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>19</v>
@@ -14277,7 +14281,7 @@
         <v>19</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>87</v>
@@ -14303,10 +14307,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14332,14 +14336,14 @@
         <v>290</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>19</v>
@@ -14388,7 +14392,7 @@
         <v>19</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -14414,10 +14418,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14443,16 +14447,16 @@
         <v>290</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>19</v>
@@ -14501,7 +14505,7 @@
         <v>19</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -14527,10 +14531,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14553,19 +14557,19 @@
         <v>19</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>19</v>
@@ -14614,7 +14618,7 @@
         <v>19</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -14640,10 +14644,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14669,14 +14673,14 @@
         <v>284</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>19</v>
@@ -14725,7 +14729,7 @@
         <v>19</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -14751,10 +14755,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14860,10 +14864,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14971,10 +14975,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15084,10 +15088,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15110,19 +15114,19 @@
         <v>19</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>19</v>
@@ -15171,7 +15175,7 @@
         <v>19</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>87</v>
@@ -15197,10 +15201,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15226,14 +15230,14 @@
         <v>205</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>19</v>
@@ -15261,10 +15265,10 @@
         <v>210</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>19</v>
@@ -15282,7 +15286,7 @@
         <v>19</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -15308,10 +15312,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15334,17 +15338,17 @@
         <v>19</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>19</v>
@@ -15393,7 +15397,7 @@
         <v>19</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -15419,10 +15423,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15445,17 +15449,17 @@
         <v>19</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>19</v>
@@ -15504,7 +15508,7 @@
         <v>19</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -15530,10 +15534,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15559,14 +15563,14 @@
         <v>284</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>19</v>
@@ -15615,7 +15619,7 @@
         <v>19</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -15641,10 +15645,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15750,10 +15754,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15861,10 +15865,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15974,10 +15978,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16000,17 +16004,17 @@
         <v>19</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>19</v>
@@ -16059,7 +16063,7 @@
         <v>19</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>87</v>
@@ -16085,10 +16089,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16170,7 +16174,7 @@
         <v>19</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -16196,10 +16200,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16222,17 +16226,17 @@
         <v>19</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>19</v>
@@ -16281,7 +16285,7 @@
         <v>19</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -16307,10 +16311,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16333,17 +16337,17 @@
         <v>19</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>19</v>
@@ -16392,7 +16396,7 @@
         <v>19</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -16418,10 +16422,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16444,17 +16448,17 @@
         <v>19</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>19</v>
@@ -16503,7 +16507,7 @@
         <v>19</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -16529,10 +16533,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16555,17 +16559,17 @@
         <v>19</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>19</v>
@@ -16614,7 +16618,7 @@
         <v>19</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -16640,10 +16644,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16669,14 +16673,14 @@
         <v>205</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>19</v>
@@ -16704,10 +16708,10 @@
         <v>219</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>19</v>
@@ -16725,7 +16729,7 @@
         <v>19</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -16751,10 +16755,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16780,16 +16784,16 @@
         <v>205</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>19</v>
@@ -16817,10 +16821,10 @@
         <v>219</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>19</v>
@@ -16838,7 +16842,7 @@
         <v>19</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -16864,14 +16868,14 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
@@ -16893,16 +16897,16 @@
         <v>205</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>19</v>
@@ -16930,10 +16934,10 @@
         <v>219</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>19</v>
@@ -16951,7 +16955,7 @@
         <v>19</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>76</v>
@@ -16977,14 +16981,14 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -17006,10 +17010,10 @@
         <v>205</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17040,7 +17044,7 @@
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>19</v>
@@ -17058,7 +17062,7 @@
         <v>19</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
@@ -17084,10 +17088,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17110,17 +17114,17 @@
         <v>19</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>19</v>
@@ -17169,7 +17173,7 @@
         <v>19</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
@@ -17195,10 +17199,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17224,16 +17228,16 @@
         <v>205</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>19</v>
@@ -17261,10 +17265,10 @@
         <v>219</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>19</v>
@@ -17282,7 +17286,7 @@
         <v>19</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -17308,10 +17312,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17337,16 +17341,16 @@
         <v>205</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>19</v>
@@ -17374,10 +17378,10 @@
         <v>219</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>19</v>
@@ -17395,7 +17399,7 @@
         <v>19</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -17421,10 +17425,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17447,17 +17451,17 @@
         <v>19</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>19</v>
@@ -17506,7 +17510,7 @@
         <v>19</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -17532,10 +17536,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17558,17 +17562,17 @@
         <v>19</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>19</v>
@@ -17596,10 +17600,10 @@
         <v>219</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>19</v>
@@ -17617,7 +17621,7 @@
         <v>19</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -17635,7 +17639,7 @@
         <v>19</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>19</v>
@@ -17643,10 +17647,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17669,17 +17673,17 @@
         <v>19</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>19</v>
@@ -17728,7 +17732,7 @@
         <v>19</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -17754,10 +17758,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17780,17 +17784,17 @@
         <v>19</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>19</v>
@@ -17839,7 +17843,7 @@
         <v>19</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -17865,10 +17869,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17891,17 +17895,17 @@
         <v>19</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>19</v>
@@ -17950,7 +17954,7 @@
         <v>19</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>76</v>
@@ -17976,10 +17980,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18002,19 +18006,19 @@
         <v>19</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>19</v>
@@ -18063,7 +18067,7 @@
         <v>19</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>76</v>
@@ -18089,10 +18093,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18115,17 +18119,17 @@
         <v>19</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>19</v>
@@ -18174,7 +18178,7 @@
         <v>19</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>76</v>
@@ -18200,10 +18204,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18226,19 +18230,19 @@
         <v>19</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>19</v>
@@ -18287,7 +18291,7 @@
         <v>19</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>76</v>
@@ -18313,10 +18317,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18339,17 +18343,17 @@
         <v>19</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>19</v>
@@ -18398,7 +18402,7 @@
         <v>19</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
@@ -18424,10 +18428,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18453,10 +18457,10 @@
         <v>284</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -18507,7 +18511,7 @@
         <v>19</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
@@ -18533,10 +18537,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18642,10 +18646,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18753,10 +18757,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18866,10 +18870,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18892,19 +18896,19 @@
         <v>19</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>19</v>
@@ -18933,7 +18937,7 @@
       </c>
       <c r="Y145" s="2"/>
       <c r="Z145" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>19</v>
@@ -18951,7 +18955,7 @@
         <v>19</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>87</v>
@@ -18977,10 +18981,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19006,14 +19010,14 @@
         <v>205</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>19</v>
@@ -19042,7 +19046,7 @@
       </c>
       <c r="Y146" s="2"/>
       <c r="Z146" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>19</v>
@@ -19060,7 +19064,7 @@
         <v>19</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>76</v>
@@ -19086,10 +19090,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19173,7 +19177,7 @@
         <v>19</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>76</v>
@@ -19188,7 +19192,7 @@
         <v>99</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>19</v>
@@ -19199,10 +19203,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19228,14 +19232,14 @@
         <v>284</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>19</v>
@@ -19284,7 +19288,7 @@
         <v>19</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -19310,10 +19314,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19419,10 +19423,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19530,10 +19534,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19643,10 +19647,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19669,17 +19673,17 @@
         <v>19</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>19</v>
@@ -19728,7 +19732,7 @@
         <v>19</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>87</v>
@@ -19754,10 +19758,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19839,7 +19843,7 @@
         <v>19</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>76</v>
@@ -19865,10 +19869,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19894,14 +19898,14 @@
         <v>205</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>19</v>
@@ -19929,10 +19933,10 @@
         <v>219</v>
       </c>
       <c r="Y154" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="Z154" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>19</v>
@@ -19950,7 +19954,7 @@
         <v>19</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>76</v>
@@ -19976,10 +19980,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20005,16 +20009,16 @@
         <v>205</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>19</v>
@@ -20042,10 +20046,10 @@
         <v>219</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>19</v>
@@ -20063,7 +20067,7 @@
         <v>19</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>76</v>
@@ -20089,14 +20093,14 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -20118,16 +20122,16 @@
         <v>205</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>19</v>
@@ -20155,10 +20159,10 @@
         <v>219</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>19</v>
@@ -20176,7 +20180,7 @@
         <v>19</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>76</v>
@@ -20202,14 +20206,14 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
@@ -20231,10 +20235,10 @@
         <v>205</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -20265,7 +20269,7 @@
       </c>
       <c r="Y157" s="2"/>
       <c r="Z157" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>19</v>
@@ -20283,7 +20287,7 @@
         <v>19</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>76</v>
@@ -20309,10 +20313,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20338,16 +20342,16 @@
         <v>205</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>19</v>
@@ -20375,10 +20379,10 @@
         <v>219</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>19</v>
@@ -20396,7 +20400,7 @@
         <v>19</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>76</v>
@@ -20422,10 +20426,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20451,16 +20455,16 @@
         <v>205</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>19</v>
@@ -20488,10 +20492,10 @@
         <v>219</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>19</v>
@@ -20509,7 +20513,7 @@
         <v>19</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>76</v>
@@ -20535,10 +20539,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20561,17 +20565,17 @@
         <v>19</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>19</v>
@@ -20620,7 +20624,7 @@
         <v>19</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>76</v>
@@ -20646,10 +20650,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20672,17 +20676,17 @@
         <v>19</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>19</v>
@@ -20731,7 +20735,7 @@
         <v>19</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -20757,10 +20761,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20783,17 +20787,17 @@
         <v>19</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>19</v>
@@ -20842,7 +20846,7 @@
         <v>19</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>
@@ -20868,10 +20872,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20894,19 +20898,19 @@
         <v>19</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>19</v>
@@ -20955,7 +20959,7 @@
         <v>19</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>76</v>
@@ -20981,10 +20985,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21007,17 +21011,17 @@
         <v>19</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>19</v>
@@ -21066,7 +21070,7 @@
         <v>19</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>76</v>
@@ -21092,10 +21096,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21118,19 +21122,19 @@
         <v>19</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>19</v>
@@ -21179,7 +21183,7 @@
         <v>19</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>76</v>
@@ -21205,10 +21209,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21231,17 +21235,17 @@
         <v>19</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>19</v>
@@ -21290,7 +21294,7 @@
         <v>19</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>76</v>
@@ -21316,10 +21320,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21345,14 +21349,14 @@
         <v>284</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>19</v>
@@ -21401,7 +21405,7 @@
         <v>19</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>76</v>
@@ -21427,10 +21431,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21536,10 +21540,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21647,10 +21651,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21760,10 +21764,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21786,17 +21790,17 @@
         <v>19</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>19</v>
@@ -21845,7 +21849,7 @@
         <v>19</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>87</v>
@@ -21871,10 +21875,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21956,7 +21960,7 @@
         <v>19</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>76</v>
@@ -21982,10 +21986,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22011,14 +22015,14 @@
         <v>205</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>19</v>
@@ -22046,10 +22050,10 @@
         <v>219</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>19</v>
@@ -22067,7 +22071,7 @@
         <v>19</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>76</v>
@@ -22093,10 +22097,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22122,16 +22126,16 @@
         <v>205</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>19</v>
@@ -22159,10 +22163,10 @@
         <v>219</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>19</v>
@@ -22180,7 +22184,7 @@
         <v>19</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>76</v>
@@ -22206,10 +22210,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22235,16 +22239,16 @@
         <v>205</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>19</v>
@@ -22272,10 +22276,10 @@
         <v>219</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>19</v>
@@ -22293,7 +22297,7 @@
         <v>19</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>76</v>
@@ -22319,14 +22323,14 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -22348,10 +22352,10 @@
         <v>205</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -22382,7 +22386,7 @@
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>19</v>
@@ -22400,7 +22404,7 @@
         <v>19</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>76</v>
@@ -22426,10 +22430,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22455,16 +22459,16 @@
         <v>205</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>19</v>
@@ -22492,10 +22496,10 @@
         <v>219</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>19</v>
@@ -22513,7 +22517,7 @@
         <v>19</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>76</v>
@@ -22539,10 +22543,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22568,16 +22572,16 @@
         <v>205</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>19</v>
@@ -22605,10 +22609,10 @@
         <v>219</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>19</v>
@@ -22626,7 +22630,7 @@
         <v>19</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>76</v>
@@ -22652,10 +22656,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22678,17 +22682,17 @@
         <v>19</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>19</v>
@@ -22737,7 +22741,7 @@
         <v>19</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>76</v>
@@ -22763,10 +22767,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22789,17 +22793,17 @@
         <v>19</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>19</v>
@@ -22848,7 +22852,7 @@
         <v>19</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>76</v>
@@ -22874,10 +22878,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -22900,17 +22904,17 @@
         <v>19</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>19</v>
@@ -22959,7 +22963,7 @@
         <v>19</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>76</v>
@@ -22985,10 +22989,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23011,19 +23015,19 @@
         <v>19</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>19</v>
@@ -23072,7 +23076,7 @@
         <v>19</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>76</v>
@@ -23098,10 +23102,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23124,17 +23128,17 @@
         <v>19</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>19</v>
@@ -23183,7 +23187,7 @@
         <v>19</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>76</v>
@@ -23209,10 +23213,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23235,19 +23239,19 @@
         <v>19</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>19</v>
@@ -23296,7 +23300,7 @@
         <v>19</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>76</v>
@@ -23322,10 +23326,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23348,17 +23352,17 @@
         <v>19</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>19</v>
@@ -23407,7 +23411,7 @@
         <v>19</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>76</v>
@@ -23433,10 +23437,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23459,17 +23463,17 @@
         <v>19</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>19</v>
@@ -23518,7 +23522,7 @@
         <v>19</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>76</v>
